--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484648_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484648_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5903</v>
+        <v>9.5326</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8729</v>
+        <v>7.8152</v>
       </c>
       <c r="F2" t="n">
         <v>1.7175</v>
@@ -610,10 +610,10 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4548</v>
+        <v>1.3971</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2142</v>
+        <v>1.1565</v>
       </c>
       <c r="U2" t="n">
         <v>0.2405</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.924</v>
+        <v>5.4905</v>
       </c>
       <c r="E3" t="n">
-        <v>5.762</v>
+        <v>4.03</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.838</v>
+        <v>1.4606</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3245</v>
+        <v>2.2961</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1802</v>
+        <v>1.7321</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8556</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8375</v>
+        <v>3.591</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6412</v>
+        <v>2.065</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1962</v>
+        <v>1.526</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.513</v>
+        <v>-1.2949</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4611</v>
+        <v>-0.3329</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0519</v>
+        <v>-0.962</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4819</v>
+        <v>1.8326</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4819</v>
+        <v>2.7489</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0181</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2361</v>
+        <v>0.7217</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.218</v>
+        <v>0.0066</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.9005</v>
+        <v>0.6335</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3115</v>
+        <v>0.6335</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.306</v>
+        <v>5.3087</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0684</v>
+        <v>6.1466</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2376</v>
+        <v>-0.838</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2961</v>
+        <v>3.3245</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7321</v>
+        <v>5.1802</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5639999999999999</v>
+        <v>-1.8556</v>
       </c>
       <c r="J4" t="n">
-        <v>3.591</v>
+        <v>5.8375</v>
       </c>
       <c r="K4" t="n">
-        <v>2.065</v>
+        <v>5.6412</v>
       </c>
       <c r="L4" t="n">
-        <v>1.526</v>
+        <v>0.1962</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2949</v>
+        <v>-2.513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3329</v>
+        <v>-0.4611</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.962</v>
+        <v>-2.0519</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8326</v>
+        <v>3.4819</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7489</v>
+        <v>3.4819</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4562</v>
+        <v>0.4027</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2398</v>
+        <v>0.6207</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2164</v>
+        <v>-0.218</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6335</v>
+        <v>-1.9005</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6335</v>
+        <v>-0.3115</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9481</v>
+        <v>4.7421</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2445</v>
+        <v>4.0137</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7037</v>
+        <v>0.7284</v>
       </c>
       <c r="G5" t="n">
         <v>2.434</v>
@@ -844,13 +844,13 @@
         <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0747</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4404</v>
+        <v>0.3288</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3657</v>
+        <v>0.3904</v>
       </c>
       <c r="V5" t="n">
         <v>1.5889</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7546</v>
+        <v>2.707</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6309</v>
+        <v>4.054</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8763</v>
+        <v>-1.347</v>
       </c>
       <c r="G6" t="n">
         <v>2.5073</v>
@@ -922,13 +922,13 @@
         <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3989</v>
+        <v>1.3512</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2625</v>
+        <v>0.6855</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1364</v>
+        <v>0.6657</v>
       </c>
       <c r="V6" t="n">
         <v>-3.1674</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9159</v>
+        <v>0.457</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8583</v>
+        <v>-1.2429</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7743</v>
+        <v>1.6999</v>
       </c>
       <c r="G7" t="n">
         <v>-3.0761</v>
@@ -1000,13 +1000,13 @@
         <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5809</v>
+        <v>1.122</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2625</v>
+        <v>0.8778</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3185</v>
+        <v>0.2441</v>
       </c>
       <c r="V7" t="n">
         <v>0.945</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3241</v>
+        <v>0.0397</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1816</v>
+        <v>-0.3011</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1424</v>
+        <v>0.3408</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3186</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8059</v>
+        <v>0.2403</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4874</v>
+        <v>-0.8144</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6178</v>
+        <v>0.0367</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7527</v>
+        <v>-0.0466</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1349</v>
+        <v>0.0833</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7008</v>
+        <v>-0.6109</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0532</v>
+        <v>0.2869</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3525</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6493</v>
+        <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1924</v>
+        <v>0.4306</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7315</v>
+        <v>0.2278</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4608</v>
+        <v>0.2029</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9005</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
         <v>-1.267</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0535</v>
+        <v>0.0108</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4934</v>
+        <v>-0.1068</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4399</v>
+        <v>0.1177</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-1.3186</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2403</v>
+        <v>-1.8059</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8144</v>
+        <v>0.4874</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0367</v>
+        <v>-0.6178</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0466</v>
+        <v>-0.7527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0833</v>
+        <v>0.1349</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6109</v>
+        <v>-0.7008</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2869</v>
+        <v>-1.0532</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8977000000000001</v>
+        <v>0.3525</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0158</v>
+        <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3374</v>
+        <v>0.8792</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0355</v>
+        <v>0.4431</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3019</v>
+        <v>0.4361</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W9" t="n">
-        <v>1.267</v>
+        <v>1.9005</v>
       </c>
       <c r="X9" t="n">
         <v>-1.267</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>Y. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.5294</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7055</v>
+        <v>-0.0154</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.043</v>
+        <v>-0.514</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2004</v>
+        <v>-0.7947</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1429</v>
+        <v>-0.5672</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3433</v>
+        <v>-0.2275</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3058</v>
+        <v>0.1365</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8512</v>
+        <v>0.0433</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.157</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8946</v>
+        <v>-0.9312</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7083</v>
+        <v>-0.6106</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1863</v>
+        <v>-0.3207</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3107</v>
+        <v>-0.1012</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7315</v>
+        <v>-0.152</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4208</v>
+        <v>0.0507</v>
       </c>
       <c r="V10" t="n">
-        <v>3.157</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. MELGAR GARCIA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8922</v>
+        <v>-0.7892</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3039</v>
+        <v>-0.9939</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5883</v>
+        <v>0.2047</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7947</v>
+        <v>-2.2004</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5672</v>
+        <v>0.1429</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2275</v>
+        <v>-2.3433</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1365</v>
+        <v>-0.3058</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0433</v>
+        <v>0.8512</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09320000000000001</v>
+        <v>-1.157</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9312</v>
+        <v>-1.8946</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6106</v>
+        <v>-0.7083</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3207</v>
+        <v>-1.1863</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3665</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.464</v>
+        <v>0.27</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4404</v>
+        <v>0.4431</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0236</v>
+        <v>-0.1731</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>3.157</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5832</v>
+        <v>-1.4841</v>
       </c>
       <c r="E12" t="n">
         <v>-0.5545</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0287</v>
+        <v>-0.9296</v>
       </c>
       <c r="G12" t="n">
         <v>0.0212</v>
@@ -1390,13 +1390,13 @@
         <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3374</v>
+        <v>-0.2383</v>
       </c>
       <c r="T12" t="n">
         <v>0.0355</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3729</v>
+        <v>-0.2738</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>25.4856</v>
+        <v>25.4857</v>
       </c>
       <c r="E13" t="n">
-        <v>22.8447</v>
+        <v>22.8449</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6411</v>
+        <v>2.641</v>
       </c>
       <c r="G13" t="n">
         <v>8.631899999999998</v>
@@ -1456,7 +1456,7 @@
         <v>-5.4043</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.855999999999999</v>
+        <v>-7.856</v>
       </c>
       <c r="P13" t="n">
         <v>6.414099999999999</v>
@@ -1471,13 +1471,13 @@
         <v>6.9609</v>
       </c>
       <c r="T13" t="n">
-        <v>5.388699999999999</v>
+        <v>5.3885</v>
       </c>
       <c r="U13" t="n">
         <v>1.5721</v>
       </c>
       <c r="V13" t="n">
-        <v>3.4789</v>
+        <v>3.478899999999999</v>
       </c>
       <c r="W13" t="n">
         <v>12.0571</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>R. ROMAN MORA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1999</v>
+        <v>1.1365</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9948</v>
+        <v>2.5505</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-1.4141</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5427</v>
+        <v>2.7231</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4224</v>
+        <v>-0.3993</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9651999999999999</v>
+        <v>3.1224</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9549</v>
+        <v>5.6312</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8298</v>
+        <v>1.5789</v>
       </c>
       <c r="L14" t="n">
-        <v>0.125</v>
+        <v>4.0523</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4976</v>
+        <v>-2.9082</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4074</v>
+        <v>-1.9783</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0902</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-0.733</v>
@@ -1546,28 +1546,28 @@
         <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2532</v>
+        <v>-0.8431</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5664</v>
+        <v>-0.3318</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3131</v>
+        <v>-0.5113</v>
       </c>
       <c r="V14" t="n">
-        <v>2.2224</v>
+        <v>-0.0104</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTAÑES</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3251</v>
+        <v>0.3286</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3251</v>
+        <v>1.3217</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.9931</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3251</v>
+        <v>-0.5427</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3251</v>
+        <v>0.4224</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3251</v>
+        <v>1.9549</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3251</v>
+        <v>1.8298</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-2.4976</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.4074</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1.0902</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.733</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0.618</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.1067</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.5113</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. ROMAN MORA</t>
+          <t>L. SALVADOR MONTAÑES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3251</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7813</v>
+        <v>0.3251</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7113</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7231</v>
+        <v>0.3251</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3993</v>
+        <v>0.3251</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1224</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6312</v>
+        <v>0.3251</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5789</v>
+        <v>0.3251</v>
       </c>
       <c r="L16" t="n">
-        <v>4.0523</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9082</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9783</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9298999999999999</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.733</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9096</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.101</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8086</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>D. CHALATASHVILI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5027</v>
+        <v>-0.7647</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8417</v>
+        <v>0.9406</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3445</v>
+        <v>-1.7053</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7141999999999999</v>
+        <v>1.4334</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7879</v>
+        <v>0.6194</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0737</v>
+        <v>0.8141</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3492</v>
+        <v>2.4624</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2045</v>
+        <v>1.7123</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1447</v>
+        <v>0.7501</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.635</v>
+        <v>-1.029</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4166</v>
+        <v>-1.0929</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2184</v>
+        <v>0.064</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.8484</v>
+        <v>0.5498</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.4977</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0975</v>
+        <v>-0.8475</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4563</v>
+        <v>-0.6056</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3588</v>
+        <v>-0.2419</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5339</v>
+        <v>-1.9005</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6784</v>
+        <v>-1.0578</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1238</v>
+        <v>0.361</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8022</v>
+        <v>-1.4188</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1532</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2527</v>
+        <v>1.7879</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-1.0737</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9578</v>
+        <v>3.3492</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8328</v>
+        <v>3.2045</v>
       </c>
       <c r="L18" t="n">
-        <v>0.125</v>
+        <v>0.1447</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8047</v>
+        <v>-2.635</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-1.4166</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2246</v>
+        <v>-1.2184</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1833</v>
+        <v>-3.8484</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>-5.4977</v>
       </c>
       <c r="R18" t="n">
         <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2521</v>
+        <v>-0.4576</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7315</v>
+        <v>-0.0245</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5206</v>
+        <v>-0.4331</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.9005</v>
+        <v>2.5339</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>2.5339</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.1674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CHALATASHVILI</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.839</v>
+        <v>-1.5774</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9406</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7796</v>
+        <v>-2.1243</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4334</v>
+        <v>0.1532</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6194</v>
+        <v>0.2527</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8141</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4624</v>
+        <v>0.9578</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7123</v>
+        <v>0.8328</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7501</v>
+        <v>0.125</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.029</v>
+        <v>-0.8047</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0929</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.064</v>
+        <v>-0.2246</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5498</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9218</v>
+        <v>0.3531</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6056</v>
+        <v>0.1546</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3162</v>
+        <v>0.1985</v>
       </c>
       <c r="V19" t="n">
         <v>-1.9005</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.9005</v>
+        <v>-3.1674</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.908</v>
+        <v>-1.7652</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5525</v>
+        <v>1.7448</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4604</v>
+        <v>-3.51</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5455</v>
@@ -2014,13 +2014,13 @@
         <v>2.1991</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5903</v>
+        <v>-1.4476</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.46</v>
+        <v>-0.2677</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1303</v>
+        <v>-1.1799</v>
       </c>
       <c r="V20" t="n">
         <v>0.945</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7001</v>
+        <v>-2.3591</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8345</v>
+        <v>-2.6422</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1344</v>
+        <v>0.283</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3226</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1943</v>
+        <v>0.1467</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1652</v>
+        <v>0.0272</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0291</v>
+        <v>0.1195</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5759</v>
+        <v>-3.8751</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6078</v>
+        <v>-1.0309</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9681</v>
+        <v>-2.8443</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6954</v>
@@ -2170,13 +2170,13 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1633</v>
+        <v>-0.4625</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4955</v>
+        <v>0.0815</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6988</v>
+        <v>-4.2587</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3944</v>
+        <v>-3.2021</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3044</v>
+        <v>-1.0567</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8873</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6124</v>
+        <v>-1.1723</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4955</v>
+        <v>-0.3032</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1169</v>
+        <v>-0.8692</v>
       </c>
       <c r="V23" t="n">
         <v>1.267</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2886</v>
+        <v>-4.8355</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4595</v>
+        <v>-1.8826</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8291</v>
+        <v>-2.9529</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1547</v>
@@ -2326,13 +2326,13 @@
         <v>1.6493</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9506</v>
+        <v>-1.4976</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.046</v>
+        <v>-0.4691</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9046</v>
+        <v>-1.0285</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8892</v>
+        <v>-6.7823</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-1.6739</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.9845</v>
+        <v>-5.1084</v>
       </c>
       <c r="G25" t="n">
         <v>0.1672</v>
@@ -2404,13 +2404,13 @@
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7786999999999999</v>
+        <v>-0.1144</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0423</v>
+        <v>0.273</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2636</v>
+        <v>-0.3875</v>
       </c>
       <c r="V25" t="n">
         <v>-5.369</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-25.4857</v>
+        <v>-25.4856</v>
       </c>
       <c r="E26" t="n">
         <v>-2.6411</v>
       </c>
       <c r="F26" t="n">
-        <v>-22.8446</v>
+        <v>-22.8449</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.632000000000001</v>
+        <v>-8.632</v>
       </c>
       <c r="H26" t="n">
         <v>-7.8304</v>
@@ -2461,7 +2461,7 @@
         <v>5.404199999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>7.8559</v>
+        <v>7.855899999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-21.8923</v>
@@ -2482,13 +2482,13 @@
         <v>16.4931</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.9608</v>
+        <v>-6.960800000000001</v>
       </c>
       <c r="T26" t="n">
         <v>-1.5723</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.388400000000001</v>
+        <v>-5.3886</v>
       </c>
       <c r="V26" t="n">
         <v>-3.4791</v>
